--- a/Final_Visiting_Card_Data.xlsx
+++ b/Final_Visiting_Card_Data.xlsx
@@ -466,22 +466,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mobile: +91 98765 43210</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>arjunmehta@techflow.io</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>ARJUN MEHTA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mobile: +91 98765 43210</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>arjun mehta@techflow.io</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vikramaditya Singh</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,12 +513,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>vsingh@stratos-consulting.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>vsingh@stratos-consulting com</t>
+          <t>Stratos Consulting</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
